--- a/data/target.xlsx
+++ b/data/target.xlsx
@@ -804,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,7 +827,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>- Kolom 'Target Corporate' masih 0 - belum ada data target Corporate yang dikirim.</t>
+          <t>- Sumber: discan dari data referensi yang dikirim owner (SCOREBOARD OMSET ALL/SERVICE/GADGET).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>- Kolom 'Target Corporate' masih 0 untuk semua cabang - belum ada data target Corporate</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  yang dikirim. Isi manual kalau ada, atau biarkan 0 kalau memang belum ditetapkan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>- Kuartal berikutnya (Okt-Des 2026 dst), ganti angka di sini dengan target kuartal yang baru</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  lalu upload ulang file ini di sidebar dashboard (4. Target).</t>
         </is>
       </c>
     </row>
